--- a/excel-imports/student_performance.xlsx
+++ b/excel-imports/student_performance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\school-ceo-dashboard review 1\school-ceo-dashboard\excel-imports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E5328B-17DA-4F6A-8F08-036FE7603711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{268C5EE9-55DD-4B35-987D-A132A69E69B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -577,7 +577,7 @@
         <v>0.85</v>
       </c>
       <c r="F2" s="1">
-        <v>0.56000000000000005</v>
+        <v>0.76</v>
       </c>
       <c r="G2" s="1">
         <v>0.81</v>

--- a/excel-imports/student_performance.xlsx
+++ b/excel-imports/student_performance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\school-ceo-dashboard review 1\school-ceo-dashboard\excel-imports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{268C5EE9-55DD-4B35-987D-A132A69E69B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BCB8823-CC9A-419E-8287-185B0E2A3CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="54">
   <si>
     <t>Name</t>
   </si>
@@ -140,12 +140,6 @@
   </si>
   <si>
     <t>Low Risk (0%)</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>0%</t>
   </si>
   <si>
     <t>Linda Miller</t>
@@ -528,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -557,7 +551,7 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
@@ -580,7 +574,7 @@
         <v>0.76</v>
       </c>
       <c r="G2" s="1">
-        <v>0.81</v>
+        <v>0.85</v>
       </c>
       <c r="H2" t="s">
         <v>13</v>
@@ -715,31 +709,31 @@
       <c r="C7" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" t="s">
-        <v>41</v>
+      <c r="D7" s="1">
+        <v>0.89</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.78</v>
       </c>
       <c r="I7" s="1">
-        <v>0</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
         <v>22</v>
@@ -748,16 +742,16 @@
         <v>23</v>
       </c>
       <c r="E8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" t="s">
         <v>44</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
         <v>45</v>
-      </c>
-      <c r="G8" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8" t="s">
-        <v>47</v>
       </c>
       <c r="I8" s="1">
         <v>0.91</v>
@@ -765,32 +759,40 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
         <v>48</v>
       </c>
-      <c r="B9" t="s">
+      <c r="D9" t="s">
         <v>49</v>
-      </c>
-      <c r="C9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" t="s">
-        <v>51</v>
       </c>
       <c r="E9" t="s">
         <v>35</v>
       </c>
       <c r="F9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" t="s">
         <v>52</v>
-      </c>
-      <c r="G9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H9" t="s">
-        <v>54</v>
       </c>
       <c r="I9" s="1">
         <v>0.85</v>
       </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
